--- a/tests/realSuite/Piano-viaggi-SNOWBOARD-FONDO-29-GENNAIO-CON-VETTORE/input.xlsx
+++ b/tests/realSuite/Piano-viaggi-SNOWBOARD-FONDO-29-GENNAIO-CON-VETTORE/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -676,7 +676,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IS DA VINCI TRENTO</t>
+          <t>IS BONPORTI TRENTO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -685,33 +685,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IS ENAIP CLES</t>
+          <t>IS DA VINCI TRENTO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cles, Piazza Fiera</t>
+          <t>Trento, Park Area Ex Italcementi</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IS ENAIP OSSANA</t>
+          <t>IS ENAIP CLES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ossana, Via S. Antonio</t>
+          <t>Cles, Piazza Fiera</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -721,121 +721,196 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IS ENAIP VILLAZZANO</t>
+          <t>IS ENAIP OSSANA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Trento, Park Area Ex Italcementi</t>
+          <t>Ossana, Via S. Antonio</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IS GUETTI TIONE</t>
+          <t>IS ENAIP VILLAZZANO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tione, Stazione autocorriere</t>
+          <t>Trento, Park Area Ex Italcementi</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IS MAFFEI RIVA DEL GARDA</t>
+          <t>IS GUETTI TIONE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Riva del Garda, Stazione autocorriere</t>
+          <t>Tione, Stazione autocorriere</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IS MARCONI ROVERETO</t>
+          <t>IS MAFFEI RIVA DEL GARDA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rovereto, Via Monti, 1</t>
+          <t>Riva del Garda, Stazione autocorriere</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IS PERGINE 2</t>
+          <t>IS MARCONI ROVERETO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pergine, Via Dante, Fermata Tentazioni</t>
+          <t>Rovereto, Via Monti, 1</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IS PRIMIERO</t>
+          <t>IS PERGINE 2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sovramonte, Loc. Ponte Oltra, Fermata Trentino Trasporti</t>
+          <t>Pergine, Via Dante, Fermata Tentazioni</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IS ROSA BIANCA</t>
+          <t>IS PILATI CLES</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cavalese, stazione autocorriere</t>
+          <t>Cles, Piazza Fiera</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>IS PRIMIERO</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fiera di Primiero, Stazione Autocorriere</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>IS PRIMIERO</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sovramonte, Loc. Ponte Oltra, Fermata Trentino Trasporti</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>IS ROSA BIANCA</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Cavalese, stazione autocorriere</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>IS ROSA BIANCA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>Predazzo, Fermata Bus Corso Degasperi</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C31" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>IS ROVERETO FONTANA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Rovereto, Parcheggio - Stadio Quercia</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>IS RUSSEL CLES</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cles, Piazza Fiera</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
